--- a/_scotuswatch/stat_pack_OT23/statpack_replication/attorney_information_feldman/AA-FINAL.xlsx
+++ b/_scotuswatch/stat_pack_OT23/statpack_replication/attorney_information_feldman/AA-FINAL.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vikramnarasimhan/Desktop/StatPack Files/StatPack Data/Test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jake Truscott\Documents\GitHub\jaketruscott.github.io\_scotuswatch\stat_pack_OT23\statpack_replication\attorney_information_feldman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C10CDF8A-D3B2-6C44-A063-4CB6213C6652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8FAA90-4BAD-4BD3-8FD6-6AB6E5D9EE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28740" windowHeight="16300" xr2:uid="{FBE38F41-1535-1943-ACE3-5ADE80261526}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FBE38F41-1535-1943-ACE3-5ADE80261526}"/>
   </bookViews>
   <sheets>
     <sheet name="Attorney Analysis" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
     <author>tc={55B45132-04DF-44A9-978B-3ABDC6EAD390}</author>
   </authors>
   <commentList>
-    <comment ref="F76" authorId="0" shapeId="0" xr:uid="{55B45132-04DF-44A9-978B-3ABDC6EAD390}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{55B45132-04DF-44A9-978B-3ABDC6EAD390}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="351">
   <si>
     <t>Law School</t>
   </si>
@@ -823,9 +824,6 @@
     <t>NICOLE F. REAVES</t>
   </si>
   <si>
-    <t>https://www.law.virginia.edu/uvalawyer/fall-2019/article/friends-court</t>
-  </si>
-  <si>
     <t>JEAN-CLAUDE ANDRE</t>
   </si>
   <si>
@@ -938,13 +936,184 @@
   </si>
   <si>
     <t>Harvard Law School</t>
+  </si>
+  <si>
+    <t>repeater</t>
+  </si>
+  <si>
+    <t>previous_cases</t>
+  </si>
+  <si>
+    <t>arguments_2023</t>
+  </si>
+  <si>
+    <t>Romag Fasteners, Inc. v. Fossil, Inc. (2019)</t>
+  </si>
+  <si>
+    <t>Engquist v. Oregon Department of Agriculture (2007)</t>
+  </si>
+  <si>
+    <t>Dollar General Corporation v. Mississippi Band of Choctaw Indians (2015)</t>
+  </si>
+  <si>
+    <t>Michigan v. Bay Mills Indian Community (2013)</t>
+  </si>
+  <si>
+    <t>Dietz v. Bouldin (2015)</t>
+  </si>
+  <si>
+    <t>Moore v. Harper (2022)</t>
+  </si>
+  <si>
+    <t>Trump v. Hawaii (2017)</t>
+  </si>
+  <si>
+    <t>Town of Chester v. Laroe Estates, Inc. (2016)</t>
+  </si>
+  <si>
+    <t>Fulton v. City of Philadelphia (2020)</t>
+  </si>
+  <si>
+    <t>Endrew F. v. Douglas County School District (2016)</t>
+  </si>
+  <si>
+    <t>Oneok, Inc. et al. v. Learjet, Inc. et al. (2014)</t>
+  </si>
+  <si>
+    <t>Highmark v. Allcare Management Systems (2013)</t>
+  </si>
+  <si>
+    <t>McDonough v. Smith (2018)</t>
+  </si>
+  <si>
+    <t>The American Legion v. American Humanist Association (2018)</t>
+  </si>
+  <si>
+    <t>Nestlé USA, Inc. v. Doe I (2020)</t>
+  </si>
+  <si>
+    <t>Bank of America Corp. v. City of Miami (2016)</t>
+  </si>
+  <si>
+    <t>Pottawattamie County v. McGhee (2009)</t>
+  </si>
+  <si>
+    <t>Hamdan v. Rumsfeld (2005)</t>
+  </si>
+  <si>
+    <t>Genesis Healthcare v. Symczyk (2012)</t>
+  </si>
+  <si>
+    <t>JASON C. MURRAY</t>
+  </si>
+  <si>
+    <t>SHANNON W. STEVENSON</t>
+  </si>
+  <si>
+    <t>Coinbase v. Bielski (2022)</t>
+  </si>
+  <si>
+    <t>Cruz v. Arizona (2022)</t>
+  </si>
+  <si>
+    <t>Delaware v. Pennsylvania and Wisconsin (2022)</t>
+  </si>
+  <si>
+    <t>Tyler v. Hennepin County, Minnesota (2022)</t>
+  </si>
+  <si>
+    <t>Babcock v. Kijakazi (2021)</t>
+  </si>
+  <si>
+    <t>Garland v. Dai (2020)</t>
+  </si>
+  <si>
+    <t>McKinney v. Arizona (2019)</t>
+  </si>
+  <si>
+    <t>Cyan, Inc. v. Beaver County Employees' Retirement Fund (2017)</t>
+  </si>
+  <si>
+    <t>Hall v. Hall (2017)</t>
+  </si>
+  <si>
+    <t>Bristol-Myers Squibb Co. v. Superior Court of California (2016)</t>
+  </si>
+  <si>
+    <t>Fry v. Napoleon Community Schools (2016)</t>
+  </si>
+  <si>
+    <t>Lewis v. Clarke (2016)</t>
+  </si>
+  <si>
+    <t>Kansas v. Carr (2015)</t>
+  </si>
+  <si>
+    <t>Montanile v. Board of Trustees of the National Elevator Industrial Health Benefit Plan (2015)</t>
+  </si>
+  <si>
+    <t>B&amp;B Hardware Inc. v. Hargis Industries Inc. (2014)</t>
+  </si>
+  <si>
+    <t>Department of Homeland Security v. MacLean (2014)</t>
+  </si>
+  <si>
+    <t>Kansas v. Cheever (2013)</t>
+  </si>
+  <si>
+    <t>Law v. Siegel (2013)</t>
+  </si>
+  <si>
+    <t>US Airways v. McCutchen (2012)</t>
+  </si>
+  <si>
+    <t>American Electric Power Co., Inc. v. Connecticut (2010)</t>
+  </si>
+  <si>
+    <t>Arizona Christian School Tuition Organization v. Winn (2010)</t>
+  </si>
+  <si>
+    <t>Ashcroft v. Al-Kidd (2010)</t>
+  </si>
+  <si>
+    <t>Chamber of Commerce of the United States v. Whiting (2010)</t>
+  </si>
+  <si>
+    <t>General Dynamics Corp. v. United States (2010)</t>
+  </si>
+  <si>
+    <t>National Aeronautics and Space Administration v. Nelson (2010)</t>
+  </si>
+  <si>
+    <t>City of Ontario v. Quon (2009)</t>
+  </si>
+  <si>
+    <t>Lewis v. Chicago (2009)</t>
+  </si>
+  <si>
+    <t>New Process Steel v. NLRB (2009)</t>
+  </si>
+  <si>
+    <t>United States v. Stevens (2009)</t>
+  </si>
+  <si>
+    <t>District Attorney's Office for the Third Judicial District v. Osborne (2008)</t>
+  </si>
+  <si>
+    <t>Northwest Austin Municipal Util. Dist. No. One v. Holder (2008)</t>
+  </si>
+  <si>
+    <t>Olson Grimsley</t>
+  </si>
+  <si>
+    <t>CO SG Office</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -961,14 +1130,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1003,22 +1164,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1041,9 +1200,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1081,7 +1240,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1187,7 +1346,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1329,7 +1488,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1337,7 +1496,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F76" dT="2024-05-28T01:59:15.29" personId="{8D256982-06AD-4AC7-8AE2-FB5E08C5A379}" id="{55B45132-04DF-44A9-978B-3ABDC6EAD390}">
+  <threadedComment ref="F71" dT="2024-05-28T01:59:15.29" personId="{8D256982-06AD-4AC7-8AE2-FB5E08C5A379}" id="{55B45132-04DF-44A9-978B-3ABDC6EAD390}">
     <text xml:space="preserve">Dad you told me Blatt worked in the SGs office... </text>
   </threadedComment>
 </ThreadedComments>
@@ -1345,22 +1504,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A78A9A-92AD-4C57-9A99-936A2AC7E495}">
-  <dimension ref="A1:O102"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <dimension ref="A1:N103"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.5" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="23.375" customWidth="1"/>
+    <col min="6" max="7" width="21.5" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.6640625" customWidth="1"/>
-    <col min="13" max="13" width="22.1640625" customWidth="1"/>
+    <col min="9" max="9" width="5.5" customWidth="1"/>
+    <col min="10" max="10" width="7.375" customWidth="1"/>
+    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="29.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1397,19 +1554,28 @@
       <c r="K1" t="s">
         <v>37</v>
       </c>
+      <c r="L1" t="s">
+        <v>294</v>
+      </c>
+      <c r="M1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N1" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
         <v>107</v>
@@ -1418,35 +1584,43 @@
         <v>107</v>
       </c>
       <c r="G2" t="str">
-        <f t="shared" ref="G2:G33" si="0">IF(OR(E2="Y", F2="Y"),"Y","N")</f>
+        <f>IF(OR(E2="Y", F2="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="J2" t="s">
         <v>80</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
         <v>107</v>
@@ -1455,35 +1629,43 @@
         <v>107</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E3="Y", F3="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="I3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>8</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
         <v>107</v>
@@ -1492,44 +1674,52 @@
         <v>107</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E4="Y", F4="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="I4" t="s">
         <v>113</v>
       </c>
       <c r="J4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>224</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E5="Y", F5="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H5" t="s">
@@ -1539,19 +1729,27 @@
         <v>118</v>
       </c>
       <c r="J5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>69</v>
-      </c>
-      <c r="M5" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>107</v>
@@ -1563,51 +1761,59 @@
         <v>107</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E6="Y", F6="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J6" t="s">
         <v>80</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>268</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F7" t="s">
         <v>83</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E7="Y", F7="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="I7" t="s">
         <v>118</v>
@@ -1615,20 +1821,31 @@
       <c r="J7" t="s">
         <v>80</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>107</v>
@@ -1637,29 +1854,37 @@
         <v>107</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E8="Y", F8="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H8" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="J8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
-      </c>
-      <c r="M8" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>107</v>
@@ -1671,38 +1896,46 @@
         <v>107</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="0"/>
-        <v>Y</v>
+        <f>IF(OR(E9="Y", F9="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
+        <v>237</v>
       </c>
       <c r="I9" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="J9" t="s">
         <v>80</v>
       </c>
       <c r="K9" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
         <v>2</v>
       </c>
-      <c r="M9" s="3"/>
+      <c r="N9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>107</v>
@@ -1711,29 +1944,37 @@
         <v>107</v>
       </c>
       <c r="G10" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E10="Y", F10="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I10" t="s">
         <v>118</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>107</v>
@@ -1742,35 +1983,43 @@
         <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
         <v>107</v>
       </c>
       <c r="G11" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E11="Y", F11="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H11" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="J11" t="s">
         <v>81</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>36</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
         <v>107</v>
@@ -1785,49 +2034,56 @@
         <v>107</v>
       </c>
       <c r="G12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E12="Y", F12="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H12" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="I12" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="J12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G13" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E13="Y", F13="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="I13" t="s">
         <v>118</v>
@@ -1836,22 +2092,30 @@
         <v>80</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E14" t="s">
         <v>107</v>
@@ -1860,103 +2124,127 @@
         <v>107</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E14="Y", F14="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H14" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="J14" t="s">
         <v>80</v>
       </c>
       <c r="K14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M14" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E15="Y", F15="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H15" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="J15" t="s">
         <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>7</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E16="Y", F16="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="I16" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="J16" t="s">
         <v>80</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>20</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
         <v>107</v>
@@ -1968,14 +2256,14 @@
         <v>107</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" si="0"/>
-        <v>Y</v>
+        <f>IF(OR(E17="Y", F17="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H17" t="s">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="I17" t="s">
         <v>118</v>
@@ -1984,22 +2272,30 @@
         <v>80</v>
       </c>
       <c r="K17" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>6</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>107</v>
@@ -2008,48 +2304,56 @@
         <v>107</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E18="Y", F18="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="I18" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
         <v>80</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
-      </c>
-      <c r="M18" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="1" t="s">
-        <v>89</v>
+      <c r="A19" t="s">
+        <v>228</v>
       </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
         <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E19" t="s">
         <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E19="Y", F19="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H19" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="I19" t="s">
         <v>118</v>
@@ -2058,54 +2362,69 @@
         <v>80</v>
       </c>
       <c r="K19" t="s">
-        <v>55</v>
-      </c>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>149</v>
+      <c r="A20" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
         <v>107</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E20="Y", F20="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H20" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J20" t="s">
         <v>79</v>
       </c>
       <c r="K20" t="s">
-        <v>38</v>
-      </c>
-      <c r="M20" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>146</v>
+      <c r="A21" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
@@ -2117,38 +2436,46 @@
         <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v>Y</v>
+        <f>IF(OR(E21="Y", F21="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>83</v>
@@ -2157,7 +2484,7 @@
         <v>83</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E22="Y", F22="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H22" t="s">
@@ -2170,12 +2497,21 @@
         <v>80</v>
       </c>
       <c r="K22" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>177</v>
+      <c r="A23" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
@@ -2184,16 +2520,16 @@
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="E23" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E23="Y", F23="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H23" t="s">
@@ -2203,39 +2539,46 @@
         <v>118</v>
       </c>
       <c r="J23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>7</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="0"/>
-        <v>N</v>
+        <f>IF(OR(E24="Y", F24="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H24" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="I24" t="s">
         <v>118</v>
@@ -2244,23 +2587,30 @@
         <v>80</v>
       </c>
       <c r="K24" t="s">
-        <v>41</v>
-      </c>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>29</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
         <v>83</v>
@@ -2269,184 +2619,223 @@
         <v>83</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E25="Y", F25="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H25" t="s">
         <v>117</v>
       </c>
       <c r="I25" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="J25" t="s">
         <v>80</v>
       </c>
       <c r="K25" t="s">
-        <v>52</v>
-      </c>
-      <c r="M25" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="2" t="s">
-        <v>147</v>
+      <c r="A26" t="s">
+        <v>229</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
         <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
         <v>107</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="0"/>
-        <v>Y</v>
+        <f>IF(OR(E26="Y", F26="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="I26" t="s">
         <v>118</v>
       </c>
       <c r="J26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
-      </c>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
         <v>83</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E27="Y", F27="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="I27" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J27" t="s">
         <v>80</v>
       </c>
       <c r="K27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M27" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>15</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
+        <v>246</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" t="str">
+        <f>IF(OR(E28="Y", F28="Y"),"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="H28" t="s">
+        <v>247</v>
+      </c>
+      <c r="I28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>59</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
         <v>108</v>
       </c>
-      <c r="E28" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" t="str">
-        <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H28" t="s">
-        <v>166</v>
-      </c>
-      <c r="I28" t="s">
-        <v>167</v>
-      </c>
-      <c r="J28" t="s">
-        <v>80</v>
-      </c>
-      <c r="K28" t="s">
-        <v>7</v>
-      </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" t="s">
-        <v>164</v>
-      </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
         <v>107</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="0"/>
-        <v>Y</v>
+        <f>IF(OR(E29="Y", F29="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="I29" t="s">
         <v>118</v>
       </c>
       <c r="J29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K29" t="s">
-        <v>67</v>
-      </c>
-      <c r="M29" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>7</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>107</v>
@@ -2455,35 +2844,43 @@
         <v>107</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E30="Y", F30="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H30" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="I30" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
         <v>80</v>
       </c>
       <c r="K30" t="s">
-        <v>3</v>
-      </c>
-      <c r="M30" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
         <v>107</v>
@@ -2492,35 +2889,43 @@
         <v>107</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E31="Y", F31="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H31" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="I31" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>20</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" t="s">
-        <v>152</v>
+      <c r="A32" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
         <v>107</v>
@@ -2529,29 +2934,37 @@
         <v>107</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E32="Y", F32="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H32" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="I32" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J32" t="s">
         <v>79</v>
       </c>
       <c r="K32" t="s">
-        <v>44</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="1:15">
+        <v>3</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
         <v>107</v>
@@ -2566,47 +2979,56 @@
         <v>107</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(OR(E33="Y", F33="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="I33" t="s">
-        <v>118</v>
+        <v>265</v>
       </c>
       <c r="J33" t="s">
         <v>80</v>
       </c>
       <c r="K33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>49</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" ref="G34:G65" si="1">IF(OR(E34="Y", F34="Y"),"Y","N")</f>
-        <v>N</v>
+        <f>IF(OR(E34="Y", F34="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H34" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="I34" t="s">
         <v>118</v>
@@ -2615,13 +3037,21 @@
         <v>80</v>
       </c>
       <c r="K34" t="s">
-        <v>1</v>
-      </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="A35" t="s">
-        <v>157</v>
+        <v>74</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>149</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
@@ -2630,35 +3060,43 @@
         <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E35" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E35="Y", F35="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H35" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="I35" t="s">
         <v>118</v>
       </c>
       <c r="J35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" t="s">
-        <v>183</v>
+        <v>67</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>23</v>
+      </c>
+      <c r="N35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="4" t="s">
+        <v>286</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
@@ -2667,16 +3105,16 @@
         <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>269</v>
       </c>
       <c r="E36" t="s">
         <v>83</v>
       </c>
       <c r="F36" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E36="Y", F36="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H36" t="s">
@@ -2686,56 +3124,69 @@
         <v>118</v>
       </c>
       <c r="J36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" s="3"/>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="1" t="s">
-        <v>96</v>
+        <v>292</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E37" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="1"/>
-        <v>N</v>
+        <f>IF(OR(E37="Y", F37="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H37" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="I37" t="s">
         <v>118</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
-      </c>
-      <c r="K37" t="s">
-        <v>38</v>
-      </c>
-      <c r="M37" s="3"/>
-    </row>
-    <row r="38" spans="1:15">
+        <v>80</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>34</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
         <v>107</v>
@@ -2750,103 +3201,121 @@
         <v>107</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E38="Y", F38="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="I38" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J38" t="s">
         <v>80</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
-      </c>
-      <c r="M38" s="3"/>
-    </row>
-    <row r="39" spans="1:15">
-      <c r="A39" t="s">
-        <v>189</v>
+        <v>20</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C39" t="s">
         <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E39" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
         <v>107</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E39="Y", F39="Y"),"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="H39" t="s">
+        <v>117</v>
+      </c>
+      <c r="I39" t="s">
+        <v>118</v>
+      </c>
+      <c r="J39" t="s">
+        <v>79</v>
+      </c>
+      <c r="K39" t="s">
+        <v>3</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>13</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G40" t="str">
+        <f>IF(OR(E40="Y", F40="Y"),"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="H39" t="s">
-        <v>190</v>
-      </c>
-      <c r="I39" t="s">
-        <v>191</v>
-      </c>
-      <c r="J39" t="s">
-        <v>80</v>
-      </c>
-      <c r="K39" t="s">
-        <v>57</v>
-      </c>
-      <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="1:15">
-      <c r="A40" t="s">
-        <v>192</v>
-      </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" t="s">
-        <v>108</v>
-      </c>
-      <c r="E40" t="s">
-        <v>107</v>
-      </c>
-      <c r="F40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G40" t="str">
-        <f t="shared" si="1"/>
-        <v>N</v>
-      </c>
       <c r="H40" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I40" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="J40" t="s">
         <v>79</v>
       </c>
       <c r="K40" t="s">
-        <v>6</v>
-      </c>
-      <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="1:15">
-      <c r="A41" t="s">
-        <v>195</v>
+        <v>73</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C41" t="s">
         <v>107</v>
@@ -2861,44 +3330,52 @@
         <v>107</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E41="Y", F41="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H41" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I41" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="J41" t="s">
         <v>80</v>
       </c>
       <c r="K41" t="s">
-        <v>47</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="1:15">
-      <c r="A42" t="s">
-        <v>198</v>
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
         <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="E42" t="s">
         <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E42="Y", F42="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H42" t="s">
@@ -2911,22 +3388,30 @@
         <v>80</v>
       </c>
       <c r="K42" t="s">
-        <v>70</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="1:15">
+        <v>77</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>12</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
         <v>107</v>
@@ -2935,29 +3420,37 @@
         <v>107</v>
       </c>
       <c r="G43" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E43="Y", F43="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H43" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="I43" t="s">
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s">
-        <v>59</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="1:15">
+        <v>51</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
         <v>107</v>
@@ -2972,29 +3465,37 @@
         <v>107</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E44="Y", F44="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H44" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="I44" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J44" t="s">
         <v>80</v>
       </c>
       <c r="K44" t="s">
-        <v>68</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="1:15">
+        <v>45</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>48</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
         <v>107</v>
@@ -3009,107 +3510,127 @@
         <v>107</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E45="Y", F45="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H45" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I45" t="s">
+        <v>197</v>
+      </c>
+      <c r="J45" t="s">
+        <v>80</v>
+      </c>
+      <c r="K45" t="s">
+        <v>47</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B46" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E46" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G46" t="str">
+        <f>IF(OR(E46="Y", F46="Y"),"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="H46" t="s">
+        <v>128</v>
+      </c>
+      <c r="I46" t="s">
         <v>118</v>
       </c>
-      <c r="J45" t="s">
-        <v>80</v>
-      </c>
-      <c r="K45" t="s">
-        <v>28</v>
-      </c>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
-      <c r="A46" t="s">
-        <v>206</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" t="s">
-        <v>107</v>
-      </c>
-      <c r="F46" t="s">
-        <v>107</v>
-      </c>
-      <c r="G46" t="str">
-        <f t="shared" si="1"/>
+      <c r="J46" t="s">
+        <v>80</v>
+      </c>
+      <c r="K46" t="s">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>4</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>180</v>
+      </c>
+      <c r="E47" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" t="s">
+        <v>107</v>
+      </c>
+      <c r="G47" t="str">
+        <f>IF(OR(E47="Y", F47="Y"),"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="H46" t="s">
-        <v>207</v>
-      </c>
-      <c r="I46" t="s">
-        <v>113</v>
-      </c>
-      <c r="J46" t="s">
-        <v>79</v>
-      </c>
-      <c r="K46" t="s">
-        <v>39</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="1:15">
-      <c r="A47" t="s">
-        <v>208</v>
-      </c>
-      <c r="B47" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" t="s">
-        <v>107</v>
-      </c>
-      <c r="F47" t="s">
-        <v>107</v>
-      </c>
-      <c r="G47" t="str">
-        <f t="shared" si="1"/>
-        <v>N</v>
-      </c>
       <c r="H47" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="J47" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s">
-        <v>46</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="1:15">
-      <c r="A48" t="s">
-        <v>209</v>
+        <v>3</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
         <v>107</v>
@@ -3124,82 +3645,101 @@
         <v>107</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E48="Y", F48="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H48" t="s">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="I48" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K48" t="s">
-        <v>72</v>
-      </c>
-      <c r="M48" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="E49" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F49" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
+        <f>IF(OR(E49="Y", F49="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H49" t="s">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="I49" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="J49" t="s">
         <v>80</v>
       </c>
-      <c r="M49" s="3"/>
+      <c r="K49" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="1" t="s">
-        <v>90</v>
+      <c r="A50" t="s">
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F50" t="s">
         <v>107</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
+        <f>IF(OR(E50="Y", F50="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="I50" t="s">
         <v>118</v>
@@ -3208,16 +3748,24 @@
         <v>79</v>
       </c>
       <c r="K50" t="s">
-        <v>3</v>
-      </c>
-      <c r="M50" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>106</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
         <v>107</v>
@@ -3226,35 +3774,43 @@
         <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F51" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
+        <f>IF(OR(E51="Y", F51="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H51" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="I51" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s">
-        <v>1</v>
-      </c>
-      <c r="M51" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
         <v>107</v>
@@ -3269,67 +3825,82 @@
         <v>107</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E52="Y", F52="Y"),"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="H52" t="s">
-        <v>214</v>
+      <c r="H52" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="I52" t="s">
-        <v>197</v>
+        <v>113</v>
       </c>
       <c r="J52" t="s">
         <v>80</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
-      </c>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>3</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" t="s">
-        <v>215</v>
+      <c r="A53" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E53" t="s">
         <v>107</v>
       </c>
       <c r="F53" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="1"/>
-        <v>N</v>
+        <f>IF(OR(E53="Y", F53="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H53" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="I53" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="J53" t="s">
         <v>80</v>
       </c>
       <c r="K53" t="s">
-        <v>12</v>
-      </c>
-      <c r="M53" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>30</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
         <v>107</v>
@@ -3344,35 +3915,43 @@
         <v>107</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E54="Y", F54="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H54" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="I54" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="J54" t="s">
         <v>80</v>
       </c>
       <c r="K54" t="s">
-        <v>60</v>
-      </c>
-      <c r="M54" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D55" t="s">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="E55" t="s">
         <v>107</v>
@@ -3381,35 +3960,43 @@
         <v>107</v>
       </c>
       <c r="G55" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E55="Y", F55="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H55" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="I55" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="J55" t="s">
         <v>80</v>
       </c>
       <c r="K55" t="s">
-        <v>5</v>
-      </c>
-      <c r="M55" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>45</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
         <v>107</v>
@@ -3418,48 +4005,56 @@
         <v>107</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E56="Y", F56="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H56" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="I56" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="J56" t="s">
         <v>80</v>
       </c>
       <c r="K56" t="s">
-        <v>40</v>
-      </c>
-      <c r="M56" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>3</v>
+      </c>
+      <c r="N56">
+        <v>2</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D57" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F57" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G57" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
+        <f>IF(OR(E57="Y", F57="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I57" t="s">
         <v>118</v>
@@ -3468,22 +4063,30 @@
         <v>79</v>
       </c>
       <c r="K57" t="s">
-        <v>66</v>
-      </c>
-      <c r="M57" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>2</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="E58" t="s">
         <v>107</v>
@@ -3492,85 +4095,101 @@
         <v>107</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E58="Y", F58="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H58" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="I58" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="J58" t="s">
         <v>79</v>
       </c>
       <c r="K58" t="s">
-        <v>11</v>
-      </c>
-      <c r="M58" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D59" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="E59" t="s">
         <v>107</v>
       </c>
       <c r="F59" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
+        <f>IF(OR(E59="Y", F59="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H59" t="s">
+        <v>216</v>
+      </c>
+      <c r="I59" t="s">
+        <v>140</v>
+      </c>
+      <c r="J59" t="s">
+        <v>80</v>
+      </c>
+      <c r="K59" t="s">
+        <v>12</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" t="s">
+        <v>107</v>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(OR(E60="Y", F60="Y"),"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="H60" t="s">
         <v>128</v>
-      </c>
-      <c r="I59" t="s">
-        <v>118</v>
-      </c>
-      <c r="J59" t="s">
-        <v>80</v>
-      </c>
-      <c r="K59" t="s">
-        <v>53</v>
-      </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" t="s">
-        <v>227</v>
-      </c>
-      <c r="B60" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" t="s">
-        <v>83</v>
-      </c>
-      <c r="D60" t="s">
-        <v>155</v>
-      </c>
-      <c r="E60" t="s">
-        <v>83</v>
-      </c>
-      <c r="F60" t="s">
-        <v>83</v>
-      </c>
-      <c r="G60" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
-      </c>
-      <c r="H60" t="s">
-        <v>117</v>
       </c>
       <c r="I60" t="s">
         <v>118</v>
@@ -3579,22 +4198,30 @@
         <v>80</v>
       </c>
       <c r="K60" t="s">
-        <v>1</v>
-      </c>
-      <c r="M60" s="3"/>
+        <v>75</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>230</v>
+        <v>108</v>
       </c>
       <c r="E61" t="s">
         <v>107</v>
@@ -3603,11 +4230,11 @@
         <v>107</v>
       </c>
       <c r="G61" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E61="Y", F61="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H61" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="I61" t="s">
         <v>118</v>
@@ -3616,95 +4243,117 @@
         <v>80</v>
       </c>
       <c r="K61" t="s">
-        <v>36</v>
-      </c>
-      <c r="M61" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="1" t="s">
-        <v>94</v>
+      <c r="A62" t="s">
+        <v>234</v>
       </c>
       <c r="B62" t="s">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D62" t="s">
+        <v>155</v>
+      </c>
+      <c r="E62" t="s">
+        <v>107</v>
+      </c>
+      <c r="F62" t="s">
+        <v>107</v>
+      </c>
+      <c r="G62" t="str">
+        <f>IF(OR(E62="Y", F62="Y"),"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="H62" t="s">
+        <v>235</v>
+      </c>
+      <c r="I62" t="s">
+        <v>173</v>
+      </c>
+      <c r="J62" t="s">
+        <v>80</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <v>5</v>
+      </c>
+      <c r="N62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" t="s">
         <v>108</v>
       </c>
-      <c r="E62" t="s">
-        <v>107</v>
-      </c>
-      <c r="F62" t="s">
-        <v>107</v>
-      </c>
-      <c r="G62" t="str">
-        <f t="shared" si="1"/>
+      <c r="E63" t="s">
+        <v>107</v>
+      </c>
+      <c r="F63" t="s">
+        <v>107</v>
+      </c>
+      <c r="G63" t="str">
+        <f>IF(OR(E63="Y", F63="Y"),"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="H62" t="s">
-        <v>207</v>
-      </c>
-      <c r="I62" t="s">
-        <v>118</v>
-      </c>
-      <c r="J62" t="s">
-        <v>80</v>
-      </c>
-      <c r="K62" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E63" t="s">
-        <v>107</v>
-      </c>
-      <c r="F63" t="s">
-        <v>83</v>
-      </c>
-      <c r="G63" t="str">
-        <f t="shared" si="1"/>
-        <v>Y</v>
-      </c>
       <c r="H63" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="I63" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="J63" t="s">
         <v>80</v>
       </c>
       <c r="K63" t="s">
-        <v>39</v>
+        <v>48</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="E64" t="s">
         <v>107</v>
@@ -3713,32 +4362,43 @@
         <v>107</v>
       </c>
       <c r="G64" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E64="Y", F64="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H64" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="I64" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="J64" t="s">
         <v>80</v>
       </c>
-      <c r="M64" s="3"/>
+      <c r="K64" t="s">
+        <v>68</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="1" t="s">
-        <v>91</v>
+      <c r="A65" t="s">
+        <v>285</v>
       </c>
       <c r="B65" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D65" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="E65" t="s">
         <v>107</v>
@@ -3747,29 +4407,37 @@
         <v>107</v>
       </c>
       <c r="G65" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(E65="Y", F65="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H65" t="s">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="I65" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="J65" t="s">
         <v>79</v>
       </c>
       <c r="K65" t="s">
-        <v>41</v>
-      </c>
-      <c r="M65" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="1" t="s">
-        <v>88</v>
+      <c r="A66" t="s">
+        <v>160</v>
       </c>
       <c r="B66" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="s">
         <v>83</v>
@@ -3781,14 +4449,14 @@
         <v>107</v>
       </c>
       <c r="F66" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G66" t="str">
-        <f t="shared" ref="G66:G101" si="2">IF(OR(E66="Y", F66="Y"),"Y","N")</f>
-        <v>Y</v>
+        <f>IF(OR(E66="Y", F66="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H66" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="I66" t="s">
         <v>118</v>
@@ -3797,53 +4465,69 @@
         <v>80</v>
       </c>
       <c r="K66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>36</v>
+      </c>
+      <c r="N66">
         <v>2</v>
       </c>
-      <c r="M66" s="3"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" t="s">
-        <v>231</v>
+      <c r="A67" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="B67" t="s">
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="E67" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F67" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
+        <f>IF(OR(E67="Y", F67="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I67" t="s">
         <v>118</v>
       </c>
       <c r="J67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s">
-        <v>56</v>
-      </c>
-      <c r="M67" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
         <v>107</v>
@@ -3858,48 +4542,56 @@
         <v>107</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E68="Y", F68="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H68" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="I68" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="J68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s">
-        <v>63</v>
-      </c>
-      <c r="M68" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="E69" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F69" t="s">
         <v>107</v>
       </c>
       <c r="G69" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
+        <f>IF(OR(E69="Y", F69="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H69" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="I69" t="s">
         <v>118</v>
@@ -3908,13 +4600,21 @@
         <v>79</v>
       </c>
       <c r="K69" t="s">
-        <v>76</v>
-      </c>
-      <c r="M69" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
@@ -3923,7 +4623,7 @@
         <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="E70" t="s">
         <v>107</v>
@@ -3932,66 +4632,82 @@
         <v>107</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E70="Y", F70="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I70" t="s">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="J70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s">
-        <v>11</v>
-      </c>
-      <c r="M70" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" t="s">
         <v>83</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="E71" t="s">
         <v>107</v>
       </c>
       <c r="F71" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
+        <f>IF(OR(E71="Y", F71="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H71" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="I71" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="J71" t="s">
         <v>79</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
-      </c>
-      <c r="M71" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>46</v>
+      </c>
+      <c r="N71">
+        <v>4</v>
+      </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
         <v>107</v>
@@ -4006,29 +4722,37 @@
         <v>107</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E72="Y", F72="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H72" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="I72" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="J72" t="s">
         <v>80</v>
       </c>
       <c r="K72" t="s">
-        <v>20</v>
-      </c>
-      <c r="M72" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C73" t="s">
         <v>107</v>
@@ -4037,72 +4761,88 @@
         <v>108</v>
       </c>
       <c r="E73" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F73" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G73" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
+        <f>IF(OR(E73="Y", F73="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H73" t="s">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="I73" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="J73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K73" t="s">
-        <v>5</v>
-      </c>
-      <c r="M73" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>98</v>
+      </c>
+      <c r="N73">
+        <v>3</v>
+      </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="B74" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
-        <v>246</v>
+        <v>108</v>
       </c>
       <c r="E74" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F74" t="s">
         <v>83</v>
       </c>
       <c r="G74" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E74="Y", F74="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H74" t="s">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="I74" t="s">
         <v>118</v>
       </c>
       <c r="J74" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s">
-        <v>42</v>
-      </c>
-      <c r="M74" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>5</v>
+      </c>
+      <c r="N74">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="1" t="s">
-        <v>95</v>
+      <c r="A75" t="s">
+        <v>282</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
         <v>107</v>
@@ -4117,73 +4857,85 @@
         <v>107</v>
       </c>
       <c r="G75" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E75="Y", F75="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H75" t="s">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="I75" t="s">
-        <v>118</v>
+        <v>289</v>
       </c>
       <c r="J75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s">
-        <v>75</v>
-      </c>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>121</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F76" t="s">
         <v>83</v>
       </c>
       <c r="G76" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E76="Y", F76="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H76" t="s">
-        <v>249</v>
+        <v>117</v>
       </c>
       <c r="I76" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="J76" t="s">
-        <v>79</v>
-      </c>
-      <c r="K76" t="s">
-        <v>5</v>
-      </c>
-      <c r="M76" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>9</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D77" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
         <v>107</v>
@@ -4192,48 +4944,56 @@
         <v>107</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E77="Y", F77="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H77" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
       <c r="I77" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="J77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K77" t="s">
-        <v>50</v>
-      </c>
-      <c r="M77" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>259</v>
+        <v>124</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="E78" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F78" t="s">
         <v>83</v>
       </c>
       <c r="G78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E78="Y", F78="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H78" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I78" t="s">
         <v>118</v>
@@ -4242,16 +5002,24 @@
         <v>80</v>
       </c>
       <c r="K78" t="s">
-        <v>43</v>
-      </c>
-      <c r="M78" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>105</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c r="B79" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C79" t="s">
         <v>107</v>
@@ -4260,34 +5028,43 @@
         <v>108</v>
       </c>
       <c r="E79" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F79" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G79" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
+        <f>IF(OR(E79="Y", F79="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H79" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="I79" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="J79" t="s">
         <v>80</v>
       </c>
       <c r="K79" t="s">
-        <v>74</v>
+        <v>65</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C80" t="s">
         <v>107</v>
@@ -4299,139 +5076,172 @@
         <v>107</v>
       </c>
       <c r="F80" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G80" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>258</v>
+        <f>IF(OR(E80="Y", F80="Y"),"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="H80" t="s">
+        <v>145</v>
       </c>
       <c r="I80" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J80" t="s">
         <v>80</v>
       </c>
       <c r="K80" t="s">
-        <v>35</v>
-      </c>
-      <c r="M80" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D81" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E81" t="s">
         <v>107</v>
       </c>
       <c r="F81" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G81" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
+        <f>IF(OR(E81="Y", F81="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H81" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="I81" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="J81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s">
-        <v>43</v>
-      </c>
-      <c r="M81" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>50</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E82" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F82" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G82" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
+        <f>IF(OR(E82="Y", F82="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H82" t="s">
-        <v>262</v>
+        <v>117</v>
       </c>
       <c r="I82" t="s">
-        <v>263</v>
+        <v>118</v>
       </c>
       <c r="J82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K82" t="s">
-        <v>3</v>
+        <v>61</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>5</v>
+      </c>
+      <c r="N82">
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" t="s">
-        <v>255</v>
+      <c r="A83" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C83" t="s">
         <v>83</v>
       </c>
       <c r="D83" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="E83" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F83" t="s">
         <v>83</v>
       </c>
       <c r="G83" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E83="Y", F83="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H83" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I83" t="s">
         <v>118</v>
       </c>
       <c r="J83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s">
-        <v>61</v>
-      </c>
-      <c r="M83" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>20</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
@@ -4440,75 +5250,91 @@
         <v>83</v>
       </c>
       <c r="D84" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E84" t="s">
         <v>107</v>
       </c>
       <c r="F84" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G84" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E84="Y", F84="Y"),"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="H84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I84" t="s">
+        <v>113</v>
+      </c>
+      <c r="J84" t="s">
+        <v>79</v>
+      </c>
+      <c r="K84" t="s">
+        <v>3</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>9</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>83</v>
+      </c>
+      <c r="D85" t="s">
+        <v>155</v>
+      </c>
+      <c r="E85" t="s">
+        <v>107</v>
+      </c>
+      <c r="F85" t="s">
+        <v>83</v>
+      </c>
+      <c r="G85" t="str">
+        <f>IF(OR(E85="Y", F85="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="H84" t="s">
-        <v>271</v>
-      </c>
-      <c r="I84" t="s">
-        <v>118</v>
-      </c>
-      <c r="J84" t="s">
-        <v>80</v>
-      </c>
-      <c r="K84" t="s">
-        <v>1</v>
-      </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="D85" t="s">
-        <v>108</v>
-      </c>
-      <c r="E85" t="s">
-        <v>83</v>
-      </c>
-      <c r="F85" t="s">
-        <v>107</v>
-      </c>
-      <c r="G85" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
-      </c>
       <c r="H85" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="I85" t="s">
         <v>118</v>
       </c>
       <c r="J85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s">
-        <v>71</v>
-      </c>
-      <c r="M85" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>110</v>
+      </c>
+      <c r="N85">
+        <v>3</v>
+      </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="B86" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C86" t="s">
         <v>107</v>
@@ -4523,35 +5349,43 @@
         <v>107</v>
       </c>
       <c r="G86" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E86="Y", F86="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H86" t="s">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="I86" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="J86" t="s">
         <v>80</v>
       </c>
       <c r="K86" t="s">
-        <v>49</v>
-      </c>
-      <c r="M86" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" t="s">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
         <v>83</v>
       </c>
       <c r="D87" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E87" t="s">
         <v>107</v>
@@ -4560,66 +5394,82 @@
         <v>107</v>
       </c>
       <c r="G87" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E87="Y", F87="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H87" t="s">
-        <v>274</v>
+        <v>151</v>
       </c>
       <c r="I87" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="J87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s">
-        <v>73</v>
-      </c>
-      <c r="M87" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>16</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="1" t="s">
-        <v>86</v>
+      <c r="A88" t="s">
+        <v>217</v>
       </c>
       <c r="B88" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D88" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="E88" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F88" t="s">
         <v>107</v>
       </c>
       <c r="G88" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
+        <f>IF(OR(E88="Y", F88="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H88" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="I88" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="J88" t="s">
         <v>80</v>
       </c>
       <c r="K88" t="s">
-        <v>77</v>
-      </c>
-      <c r="M88" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" t="s">
-        <v>272</v>
+        <v>202</v>
       </c>
       <c r="B89" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C89" t="s">
         <v>107</v>
@@ -4628,17 +5478,17 @@
         <v>108</v>
       </c>
       <c r="E89" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F89" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G89" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
+        <f>IF(OR(E89="Y", F89="Y"),"Y","N")</f>
+        <v>N</v>
       </c>
       <c r="H89" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="I89" t="s">
         <v>118</v>
@@ -4647,35 +5497,43 @@
         <v>80</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
-      </c>
-      <c r="M89" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="B90" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="E90" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F90" t="s">
         <v>83</v>
       </c>
       <c r="G90" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E90="Y", F90="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H90" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="I90" t="s">
         <v>118</v>
@@ -4684,13 +5542,21 @@
         <v>80</v>
       </c>
       <c r="K90" t="s">
-        <v>44</v>
-      </c>
-      <c r="M90" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>3</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B91" t="s">
         <v>3</v>
@@ -4699,7 +5565,7 @@
         <v>83</v>
       </c>
       <c r="D91" t="s">
-        <v>280</v>
+        <v>148</v>
       </c>
       <c r="E91" t="s">
         <v>107</v>
@@ -4708,34 +5574,43 @@
         <v>107</v>
       </c>
       <c r="G91" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E91="Y", F91="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H91" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="I91" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J91" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K91" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>13</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="B92" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D92" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="E92" t="s">
         <v>107</v>
@@ -4744,22 +5619,30 @@
         <v>107</v>
       </c>
       <c r="G92" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E92="Y", F92="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H92" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="I92" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="J92" t="s">
         <v>80</v>
       </c>
       <c r="K92" t="s">
-        <v>1</v>
-      </c>
-      <c r="M92" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
@@ -4781,11 +5664,11 @@
         <v>107</v>
       </c>
       <c r="G93" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E93="Y", F93="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H93" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I93" t="s">
         <v>118</v>
@@ -4796,58 +5679,73 @@
       <c r="K93" t="s">
         <v>3</v>
       </c>
-      <c r="M93" s="3"/>
-      <c r="N93" s="3"/>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <v>17</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" t="s">
-        <v>275</v>
+        <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
         <v>83</v>
       </c>
       <c r="D94" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="E94" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F94" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G94" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
+        <f>IF(OR(E94="Y", F94="Y"),"Y","N")</f>
+        <v>Y</v>
       </c>
       <c r="H94" t="s">
-        <v>276</v>
+        <v>117</v>
       </c>
       <c r="I94" t="s">
-        <v>277</v>
+        <v>118</v>
       </c>
       <c r="J94" t="s">
         <v>80</v>
       </c>
       <c r="K94" t="s">
-        <v>42</v>
-      </c>
-      <c r="M94" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <v>8</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B95" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E95" t="s">
         <v>107</v>
@@ -4856,29 +5754,37 @@
         <v>107</v>
       </c>
       <c r="G95" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E95="Y", F95="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H95" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="I95" t="s">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="J95" t="s">
         <v>80</v>
       </c>
       <c r="K95" t="s">
-        <v>23</v>
-      </c>
-      <c r="M95" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C96" t="s">
         <v>107</v>
@@ -4893,83 +5799,101 @@
         <v>107</v>
       </c>
       <c r="G96" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E96="Y", F96="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H96" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="I96" t="s">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="J96" t="s">
+        <v>80</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" t="s">
+        <v>206</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>83</v>
+      </c>
+      <c r="D97" t="s">
+        <v>127</v>
+      </c>
+      <c r="E97" t="s">
+        <v>107</v>
+      </c>
+      <c r="F97" t="s">
+        <v>107</v>
+      </c>
+      <c r="G97" t="str">
+        <f>IF(OR(E97="Y", F97="Y"),"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="H97" t="s">
+        <v>207</v>
+      </c>
+      <c r="I97" t="s">
+        <v>113</v>
+      </c>
+      <c r="J97" t="s">
         <v>79</v>
       </c>
-      <c r="K96" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B97" t="s">
-        <v>3</v>
-      </c>
-      <c r="C97" t="s">
-        <v>107</v>
-      </c>
-      <c r="D97" t="s">
-        <v>108</v>
-      </c>
-      <c r="E97" t="s">
-        <v>107</v>
-      </c>
-      <c r="F97" t="s">
-        <v>107</v>
-      </c>
-      <c r="G97" t="str">
-        <f t="shared" si="2"/>
+      <c r="K97" t="s">
+        <v>39</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98" t="s">
+        <v>126</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>83</v>
+      </c>
+      <c r="D98" t="s">
+        <v>127</v>
+      </c>
+      <c r="E98" t="s">
+        <v>107</v>
+      </c>
+      <c r="F98" t="s">
+        <v>107</v>
+      </c>
+      <c r="G98" t="str">
+        <f>IF(OR(E98="Y", F98="Y"),"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="H97" t="s">
-        <v>291</v>
-      </c>
-      <c r="I97" t="s">
-        <v>118</v>
-      </c>
-      <c r="J97" t="s">
-        <v>80</v>
-      </c>
-      <c r="K97" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
-      <c r="A98" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B98" t="s">
-        <v>4</v>
-      </c>
-      <c r="C98" t="s">
-        <v>107</v>
-      </c>
-      <c r="D98" t="s">
-        <v>108</v>
-      </c>
-      <c r="E98" t="s">
-        <v>107</v>
-      </c>
-      <c r="F98" t="s">
-        <v>107</v>
-      </c>
-      <c r="G98" t="str">
-        <f t="shared" si="2"/>
-        <v>N</v>
-      </c>
       <c r="H98" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="I98" t="s">
         <v>118</v>
@@ -4978,15 +5902,24 @@
         <v>79</v>
       </c>
       <c r="K98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
+        <v>5</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>286</v>
+        <v>192</v>
       </c>
       <c r="B99" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
         <v>107</v>
@@ -5001,34 +5934,43 @@
         <v>107</v>
       </c>
       <c r="G99" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E99="Y", F99="Y"),"Y","N")</f>
         <v>N</v>
       </c>
       <c r="H99" t="s">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="I99" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="J99" t="s">
         <v>79</v>
       </c>
       <c r="K99" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" s="5" t="s">
-        <v>287</v>
+        <v>6</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" t="s">
+        <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>108</v>
       </c>
       <c r="E100" t="s">
         <v>83</v>
@@ -5037,7 +5979,7 @@
         <v>107</v>
       </c>
       <c r="G100" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E100="Y", F100="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H100" t="s">
@@ -5050,58 +5992,419 @@
         <v>80</v>
       </c>
       <c r="K100" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" s="5" t="s">
-        <v>288</v>
+        <v>69</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>7</v>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101" t="s">
+        <v>183</v>
       </c>
       <c r="B101" t="s">
-        <v>294</v>
+        <v>1</v>
       </c>
       <c r="C101" t="s">
         <v>83</v>
       </c>
       <c r="D101" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="E101" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F101" t="s">
         <v>83</v>
       </c>
       <c r="G101" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(E101="Y", F101="Y"),"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="H101" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I101" t="s">
         <v>118</v>
       </c>
       <c r="J101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K101" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>2</v>
+      </c>
+      <c r="N101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>83</v>
+      </c>
+      <c r="D102" t="s">
+        <v>269</v>
+      </c>
+      <c r="E102" t="s">
+        <v>107</v>
+      </c>
+      <c r="F102" t="s">
+        <v>107</v>
+      </c>
+      <c r="G102" t="str">
+        <f>IF(OR(E102="Y", F102="Y"),"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="H102" t="s">
+        <v>349</v>
+      </c>
+      <c r="I102" t="s">
+        <v>167</v>
+      </c>
+      <c r="J102" t="s">
+        <v>80</v>
+      </c>
+      <c r="K102" t="s">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="A103" t="s">
+        <v>317</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" t="s">
+        <v>108</v>
+      </c>
+      <c r="E103" t="s">
+        <v>107</v>
+      </c>
+      <c r="F103" t="s">
+        <v>107</v>
+      </c>
+      <c r="G103" t="str">
+        <f>IF(OR(E103="Y", F103="Y"),"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="H103" t="s">
+        <v>350</v>
+      </c>
+      <c r="I103" t="s">
+        <v>167</v>
+      </c>
+      <c r="J103" t="s">
+        <v>79</v>
+      </c>
+      <c r="K103" t="s">
+        <v>11</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K96">
-    <sortCondition ref="B2:B96"/>
-    <sortCondition ref="A2:A96"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L101">
+    <sortCondition ref="A2:A101"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="O45" r:id="rId1" xr:uid="{74082985-A092-4A3A-915D-0665AE5DD7E6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B49CAF-A5CE-4DA8-B880-DE491BAEC0E6}">
+  <dimension ref="A1:A50"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>